--- a/V361 Excel.xlsx
+++ b/V361 Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\V361\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C3CAFC-C846-4885-B01B-CF0476E6DEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4744F758-5559-40AB-BF08-946C1E32B57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4EB5057D-499F-4D85-ACE4-D39C06C049EC}"/>
   </bookViews>
@@ -1654,6 +1654,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
